--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.81030928651636</v>
+        <v>5.331675259058908</v>
       </c>
       <c r="D2" t="n">
-        <v>33.07704780350577</v>
+        <v>5.375020268069688</v>
       </c>
       <c r="E2" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F2" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.9176490564061</v>
+        <v>8.924117971665991</v>
       </c>
       <c r="D3" t="n">
-        <v>54.85836936743011</v>
+        <v>8.914485022207392</v>
       </c>
       <c r="E3" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F3" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.98583673303521</v>
+        <v>4.060198469118222</v>
       </c>
       <c r="D4" t="n">
-        <v>24.62476339241799</v>
+        <v>4.001524051267923</v>
       </c>
       <c r="E4" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F4" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.33221261735535</v>
+        <v>9.316484550320245</v>
       </c>
       <c r="D5" t="n">
-        <v>53.55700130334664</v>
+        <v>8.703012711793829</v>
       </c>
       <c r="E5" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F5" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.65563139633556</v>
+        <v>5.144040101904528</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2944206764573</v>
+        <v>5.085343359924312</v>
       </c>
       <c r="E6" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F6" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.48015080276678</v>
+        <v>9.828024505449601</v>
       </c>
       <c r="D7" t="n">
-        <v>56.76576720308423</v>
+        <v>9.224437170501188</v>
       </c>
       <c r="E7" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F7" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.48210162183087</v>
+        <v>10.15334151354752</v>
       </c>
       <c r="D8" t="n">
-        <v>59.04656005058053</v>
+        <v>9.595066008219337</v>
       </c>
       <c r="E8" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F8" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>80.46099242311696</v>
+        <v>13.07491126875651</v>
       </c>
       <c r="D9" t="n">
-        <v>77.54718369038568</v>
+        <v>12.60141734968767</v>
       </c>
       <c r="E9" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F9" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.02780511822387</v>
+        <v>6.342018331711379</v>
       </c>
       <c r="D10" t="n">
-        <v>26.14651352854726</v>
+        <v>4.248808448388931</v>
       </c>
       <c r="E10" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F10" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>64.78466701224596</v>
+        <v>10.52750838948997</v>
       </c>
       <c r="D11" t="n">
-        <v>62.82922361801347</v>
+        <v>10.20974883792719</v>
       </c>
       <c r="E11" t="n">
-        <v>16.91197975203602</v>
+        <v>2.748196709705853</v>
       </c>
       <c r="F11" t="n">
-        <v>17.01606777834987</v>
+        <v>2.765111013981854</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
